--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/RHODE_ISLAND_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/RHODE_ISLAND_2018.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C30">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C77">
